--- a/hira_material_automation/output/monthly/202601_202605__all_suture_anchor__040021__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202605__all_suture_anchor__040021__normalized.xlsx
@@ -431,7 +431,7 @@
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -486,7 +486,11 @@
           <t>040021</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ALL SUTURE ANCHOR</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>9265</t>
@@ -519,7 +523,11 @@
           <t>040021</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ALL SUTURE ANCHOR</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>8336</t>
@@ -552,7 +560,11 @@
           <t>040021</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ALL SUTURE ANCHOR</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>8789</t>
@@ -625,7 +637,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-04T22:06:34</t>
+          <t>2026-05-14T22:14:48</t>
         </is>
       </c>
     </row>
@@ -637,7 +649,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>32dd5fb1fb3b09c8385161e842378140f9074fb0ef7c7bb873f92113700778f3</t>
+          <t>c757ecb57a80faeae3c6509fadf058b76a5a01938d2af7a8b6faabe93e1a5f7a</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202605__all_suture_anchor__040021__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202605__all_suture_anchor__040021__normalized.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-14T22:14:48</t>
+          <t>2026-05-24T21:59:09</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>c757ecb57a80faeae3c6509fadf058b76a5a01938d2af7a8b6faabe93e1a5f7a</t>
+          <t>553378f30525072c73cddb902d685ab1fe681bef522174be082923770030ef6b</t>
         </is>
       </c>
     </row>
